--- a/Knockouts/5thAndBelow.xlsx
+++ b/Knockouts/5thAndBelow.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\USER-PC\Ravens\Senior Open 2026\Knockouts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Ravens Seniors\Knockouts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349CC481-1B6A-461C-AE87-1EE41E506350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CC7C137-5301-4750-9B23-F21F034F7CE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="585" yWindow="345" windowWidth="20370" windowHeight="10905" activeTab="1" xr2:uid="{6F46E828-8FFD-4531-838C-1A16471CA10A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" activeTab="1" xr2:uid="{6F46E828-8FFD-4531-838C-1A16471CA10A}"/>
   </bookViews>
   <sheets>
     <sheet name="Knockout Matches" sheetId="1" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="49">
   <si>
     <t>Match</t>
   </si>
@@ -136,54 +136,12 @@
     <t>Saturday</t>
   </si>
   <si>
-    <t>G7R</t>
-  </si>
-  <si>
     <t>G2R</t>
   </si>
   <si>
-    <t>G6W</t>
-  </si>
-  <si>
-    <t>G8W</t>
-  </si>
-  <si>
-    <t>G5R</t>
-  </si>
-  <si>
-    <t>G3R</t>
-  </si>
-  <si>
-    <t>G9R</t>
-  </si>
-  <si>
-    <t>G4W</t>
-  </si>
-  <si>
-    <t>G3W</t>
-  </si>
-  <si>
-    <t>G8R</t>
-  </si>
-  <si>
     <t>G1R</t>
   </si>
   <si>
-    <t>G4R</t>
-  </si>
-  <si>
-    <t>G5W</t>
-  </si>
-  <si>
-    <t>G7W</t>
-  </si>
-  <si>
-    <t>G9W</t>
-  </si>
-  <si>
-    <t>G6R</t>
-  </si>
-  <si>
     <t>Day</t>
   </si>
   <si>
@@ -194,6 +152,63 @@
   </si>
   <si>
     <t>Table</t>
+  </si>
+  <si>
+    <t>Shakeel Hendricks</t>
+  </si>
+  <si>
+    <t>Goodwood</t>
+  </si>
+  <si>
+    <t>Jyante Jacobs</t>
+  </si>
+  <si>
+    <t>Ravens</t>
+  </si>
+  <si>
+    <t>Angeline Wood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mujaid Hoffman </t>
+  </si>
+  <si>
+    <t>Community House</t>
+  </si>
+  <si>
+    <t>Andre Taljaard</t>
+  </si>
+  <si>
+    <t>Yusuf Ebrahim</t>
+  </si>
+  <si>
+    <t>Gideon Stompies</t>
+  </si>
+  <si>
+    <t>Sabri De Sani</t>
+  </si>
+  <si>
+    <t>NEXUS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scelo Mkhetho </t>
+  </si>
+  <si>
+    <t>CPUT</t>
+  </si>
+  <si>
+    <t>Enrico Louw</t>
+  </si>
+  <si>
+    <t>Lawrence Omadeli</t>
+  </si>
+  <si>
+    <t>Pedro Fortuin</t>
+  </si>
+  <si>
+    <t>Jihaan Jacobs</t>
+  </si>
+  <si>
+    <t>Felix Monday</t>
   </si>
 </sst>
 </file>
@@ -919,16 +934,16 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="K1" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="L1" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="M1" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -1005,10 +1020,10 @@
       </c>
       <c r="D4" t="str" cm="1">
         <f t="array" ref="D4:F4">'Knockout Grid'!A13:C13</f>
-        <v>G5R</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
+        <v>Yusuf Ebrahim</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Community House</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -1046,10 +1061,10 @@
       </c>
       <c r="G5" t="str" cm="1">
         <f t="array" ref="G5:I5">'Knockout Grid'!A18:C18</f>
-        <v>G8W</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
+        <v>Lawrence Omadeli</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Community House</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1067,10 +1082,10 @@
       </c>
       <c r="D6" t="str" cm="1">
         <f t="array" ref="D6:F6">'Knockout Grid'!A21:C21</f>
-        <v>G6W</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
+        <v>Gideon Stompies</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Ravens</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1108,10 +1123,10 @@
       </c>
       <c r="G7" t="str" cm="1">
         <f t="array" ref="G7:I7">'Knockout Grid'!A26:C26</f>
-        <v>G4R</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
+        <v xml:space="preserve">Mujaid Hoffman </v>
+      </c>
+      <c r="H7" t="str">
+        <v>Community House</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1129,20 +1144,20 @@
       </c>
       <c r="D8" t="str" cm="1">
         <f t="array" ref="D8:F8">'Knockout Grid'!A29:C29</f>
-        <v>G7R</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
+        <v>Enrico Louw</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Goodwood</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8" t="str" cm="1">
         <f t="array" ref="G8:I8">'Knockout Grid'!A30:C30</f>
-        <v>G9R</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
+        <v>Felix Monday</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Community House</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1182,10 +1197,10 @@
       </c>
       <c r="G9" t="str" cm="1">
         <f t="array" ref="G9:I9">'Knockout Grid'!A34:C34</f>
-        <v>G3W</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
+        <v>Shakeel Hendricks</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Goodwood</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1203,10 +1218,10 @@
       </c>
       <c r="D10" t="str" cm="1">
         <f t="array" ref="D10:F10">'Knockout Grid'!A37:C37</f>
-        <v>G4W</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
+        <v>Angeline Wood</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Ravens</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1244,10 +1259,10 @@
       </c>
       <c r="G11" t="str" cm="1">
         <f t="array" ref="G11:I11">'Knockout Grid'!A42:C42</f>
-        <v>G9W</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
+        <v>Jihaan Jacobs</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Ravens</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -1265,10 +1280,10 @@
       </c>
       <c r="D12" t="str" cm="1">
         <f t="array" ref="D12:F12">'Knockout Grid'!A45:C45</f>
-        <v>G6R</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
+        <v>Sabri De Sani</v>
+      </c>
+      <c r="E12" t="str">
+        <v>NEXUS</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1306,10 +1321,10 @@
       </c>
       <c r="G13" t="str" cm="1">
         <f t="array" ref="G13:I13">'Knockout Grid'!A50:C50</f>
-        <v>G7W</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
+        <v xml:space="preserve">Scelo Mkhetho </v>
+      </c>
+      <c r="H13" t="str">
+        <v>CPUT</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1327,10 +1342,10 @@
       </c>
       <c r="D14" t="str" cm="1">
         <f t="array" ref="D14:F14">'Knockout Grid'!A53:C53</f>
-        <v>G5W</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
+        <v>Andre Taljaard</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Goodwood</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1368,10 +1383,10 @@
       </c>
       <c r="G15" t="str" cm="1">
         <f t="array" ref="G15:I15">'Knockout Grid'!A58:C58</f>
-        <v>G3R</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
+        <v>Jyante Jacobs</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Ravens</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -1399,10 +1414,10 @@
       </c>
       <c r="G16" t="str" cm="1">
         <f t="array" ref="G16:I16">'Knockout Grid'!A62:C62</f>
-        <v>G8R</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
+        <v>Pedro Fortuin</v>
+      </c>
+      <c r="H16" t="str">
+        <v>Goodwood</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -1504,22 +1519,22 @@
       <c r="C19">
         <v>16</v>
       </c>
-      <c r="D19" cm="1">
+      <c r="D19" t="str" cm="1">
         <f t="array" ref="D19:F19">'Knockout Grid'!F15:H15</f>
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
+        <v>Yusuf Ebrahim</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Community House</v>
       </c>
       <c r="F19">
         <v>0</v>
       </c>
-      <c r="G19" cm="1">
+      <c r="G19" t="str" cm="1">
         <f t="array" ref="G19:I19">'Knockout Grid'!F16:H16</f>
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
+        <v>Lawrence Omadeli</v>
+      </c>
+      <c r="H19" t="str">
+        <v>Community House</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1547,22 +1562,22 @@
       <c r="C20">
         <v>16</v>
       </c>
-      <c r="D20" cm="1">
+      <c r="D20" t="str" cm="1">
         <f t="array" ref="D20:F20">'Knockout Grid'!F23:H23</f>
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
+        <v>Gideon Stompies</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Ravens</v>
       </c>
       <c r="F20">
         <v>0</v>
       </c>
-      <c r="G20" cm="1">
+      <c r="G20" t="str" cm="1">
         <f t="array" ref="G20:I20">'Knockout Grid'!F24:H24</f>
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
+        <v xml:space="preserve">Mujaid Hoffman </v>
+      </c>
+      <c r="H20" t="str">
+        <v>Community House</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -1600,12 +1615,12 @@
       <c r="F21">
         <v>0</v>
       </c>
-      <c r="G21" cm="1">
+      <c r="G21" t="str" cm="1">
         <f t="array" ref="G21:I21">'Knockout Grid'!F32:H32</f>
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
+        <v>Shakeel Hendricks</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Goodwood</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1633,12 +1648,12 @@
       <c r="C22">
         <v>16</v>
       </c>
-      <c r="D22" cm="1">
+      <c r="D22" t="str" cm="1">
         <f t="array" ref="D22:F22">'Knockout Grid'!F39:H39</f>
-        <v>0</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
+        <v>Angeline Wood</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Ravens</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1676,22 +1691,22 @@
       <c r="C23">
         <v>16</v>
       </c>
-      <c r="D23" cm="1">
+      <c r="D23" t="str" cm="1">
         <f t="array" ref="D23:F23">'Knockout Grid'!F47:H47</f>
-        <v>0</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
+        <v>Sabri De Sani</v>
+      </c>
+      <c r="E23" t="str">
+        <v>NEXUS</v>
       </c>
       <c r="F23">
         <v>0</v>
       </c>
-      <c r="G23" cm="1">
+      <c r="G23" t="str" cm="1">
         <f t="array" ref="G23:I23">'Knockout Grid'!F48:H48</f>
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
+        <v xml:space="preserve">Scelo Mkhetho </v>
+      </c>
+      <c r="H23" t="str">
+        <v>CPUT</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1719,22 +1734,22 @@
       <c r="C24">
         <v>16</v>
       </c>
-      <c r="D24" cm="1">
+      <c r="D24" t="str" cm="1">
         <f t="array" ref="D24:F24">'Knockout Grid'!F55:H55</f>
-        <v>0</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
+        <v>Andre Taljaard</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Goodwood</v>
       </c>
       <c r="F24">
         <v>0</v>
       </c>
-      <c r="G24" cm="1">
+      <c r="G24" t="str" cm="1">
         <f t="array" ref="G24:I24">'Knockout Grid'!F56:H56</f>
-        <v>0</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
+        <v>Jyante Jacobs</v>
+      </c>
+      <c r="H24" t="str">
+        <v>Ravens</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -2320,7 +2335,7 @@
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="11"/>
@@ -2361,9 +2376,11 @@
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="10"/>
+        <v>38</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>36</v>
+      </c>
       <c r="C13" s="11"/>
       <c r="D13" s="2"/>
       <c r="F13" s="6" t="s">
@@ -2402,8 +2419,12 @@
     <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="D15" s="4"/>
       <c r="E15" s="5"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="10"/>
+      <c r="F15" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>36</v>
+      </c>
       <c r="H15" s="11"/>
       <c r="I15" s="5"/>
       <c r="N15" s="4"/>
@@ -2419,8 +2440,12 @@
         <v>4</v>
       </c>
       <c r="D16" s="4"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="10"/>
+      <c r="F16" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>36</v>
+      </c>
       <c r="H16" s="11"/>
       <c r="N16" s="4"/>
     </row>
@@ -2447,9 +2472,11 @@
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" s="10"/>
+        <v>45</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>36</v>
+      </c>
       <c r="C18" s="11"/>
       <c r="N18" s="4"/>
       <c r="P18">
@@ -2488,9 +2515,11 @@
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="10"/>
+        <v>39</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="C21" s="11"/>
       <c r="D21" s="2"/>
       <c r="F21" s="6" t="s">
@@ -2533,8 +2562,12 @@
       <c r="C23" s="13"/>
       <c r="D23" s="4"/>
       <c r="E23" s="5"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="10"/>
+      <c r="F23" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="H23" s="11"/>
       <c r="I23" s="2"/>
       <c r="N23" s="4"/>
@@ -2551,8 +2584,12 @@
         <v>6</v>
       </c>
       <c r="D24" s="4"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="10"/>
+      <c r="F24" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>36</v>
+      </c>
       <c r="H24" s="11"/>
       <c r="I24" s="1"/>
       <c r="N24" s="4"/>
@@ -2583,7 +2620,9 @@
       <c r="A26" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B26" s="10"/>
+      <c r="B26" s="10" t="s">
+        <v>36</v>
+      </c>
       <c r="C26" s="11"/>
       <c r="I26" s="4"/>
       <c r="K26">
@@ -2637,9 +2676,11 @@
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B29" s="10"/>
+        <v>44</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>31</v>
+      </c>
       <c r="C29" s="11"/>
       <c r="D29" s="2"/>
       <c r="F29" s="6" t="s">
@@ -2659,9 +2700,11 @@
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="10"/>
+        <v>48</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>36</v>
+      </c>
       <c r="C30" s="11"/>
       <c r="D30" s="3"/>
       <c r="F30">
@@ -2696,8 +2739,12 @@
         <v>8</v>
       </c>
       <c r="D32" s="4"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="10"/>
+      <c r="F32" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>31</v>
+      </c>
       <c r="H32" s="11"/>
       <c r="S32" s="4"/>
     </row>
@@ -2712,9 +2759,11 @@
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B34" s="10"/>
+        <v>30</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>31</v>
+      </c>
       <c r="C34" s="11"/>
       <c r="S34" s="4"/>
       <c r="U34" s="6" t="s">
@@ -2754,9 +2803,11 @@
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B37" s="10"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="C37" s="11"/>
       <c r="D37" s="2"/>
       <c r="F37" s="6" t="s">
@@ -2795,8 +2846,12 @@
     <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="D39" s="4"/>
       <c r="E39" s="5"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="10"/>
+      <c r="F39" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="H39" s="11"/>
       <c r="I39" s="2"/>
       <c r="S39" s="4"/>
@@ -2842,9 +2897,11 @@
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B42" s="10"/>
+        <v>47</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="C42" s="11"/>
       <c r="I42" s="4"/>
       <c r="K42">
@@ -2888,9 +2945,11 @@
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A45" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="10"/>
+        <v>40</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>41</v>
+      </c>
       <c r="C45" s="11"/>
       <c r="D45" s="2"/>
       <c r="F45" s="6" t="s">
@@ -2930,8 +2989,12 @@
     <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="D47" s="4"/>
       <c r="E47" s="5"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="10"/>
+      <c r="F47" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G47" s="10" t="s">
+        <v>41</v>
+      </c>
       <c r="H47" s="11"/>
       <c r="I47" s="5"/>
       <c r="N47" s="4"/>
@@ -2948,8 +3011,12 @@
         <v>12</v>
       </c>
       <c r="D48" s="4"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="10"/>
+      <c r="F48" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G48" s="10" t="s">
+        <v>43</v>
+      </c>
       <c r="H48" s="11"/>
       <c r="N48" s="4"/>
       <c r="S48" s="4"/>
@@ -2966,9 +3033,11 @@
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B50" s="10"/>
+        <v>42</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>43</v>
+      </c>
       <c r="C50" s="11"/>
       <c r="N50" s="4"/>
       <c r="P50" s="6" t="s">
@@ -3009,9 +3078,11 @@
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B53" s="10"/>
+        <v>37</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>31</v>
+      </c>
       <c r="C53" s="11"/>
       <c r="D53" s="2"/>
       <c r="F53" s="6" t="s">
@@ -3050,8 +3121,12 @@
     <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="D55" s="4"/>
       <c r="E55" s="5"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="10"/>
+      <c r="F55" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G55" s="10" t="s">
+        <v>31</v>
+      </c>
       <c r="H55" s="11"/>
       <c r="I55" s="2"/>
       <c r="N55" s="4"/>
@@ -3067,8 +3142,12 @@
         <v>14</v>
       </c>
       <c r="D56" s="4"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="10"/>
+      <c r="F56" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G56" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="H56" s="11"/>
       <c r="I56" s="1"/>
       <c r="N56" s="4"/>
@@ -3097,9 +3176,11 @@
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B58" s="10"/>
+        <v>32</v>
+      </c>
+      <c r="B58" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="C58" s="11"/>
       <c r="I58" s="4"/>
       <c r="K58">
@@ -3150,7 +3231,7 @@
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61" s="9" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B61" s="10"/>
       <c r="C61" s="11"/>
@@ -3170,9 +3251,11 @@
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A62" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B62" s="10"/>
+        <v>46</v>
+      </c>
+      <c r="B62" s="10" t="s">
+        <v>31</v>
+      </c>
       <c r="C62" s="11"/>
       <c r="D62" s="3"/>
       <c r="F62">

--- a/Knockouts/5thAndBelow.xlsx
+++ b/Knockouts/5thAndBelow.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Ravens Seniors\Knockouts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CC7C137-5301-4750-9B23-F21F034F7CE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D2FC43B-71AC-483C-9B41-649DEBBE3F03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" activeTab="1" xr2:uid="{6F46E828-8FFD-4531-838C-1A16471CA10A}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="50">
   <si>
     <t>Match</t>
   </si>
@@ -103,12 +103,6 @@
     <t>Bye</t>
   </si>
   <si>
-    <t>G1W</t>
-  </si>
-  <si>
-    <t>G2W</t>
-  </si>
-  <si>
     <t>bye</t>
   </si>
   <si>
@@ -136,12 +130,6 @@
     <t>Saturday</t>
   </si>
   <si>
-    <t>G2R</t>
-  </si>
-  <si>
-    <t>G1R</t>
-  </si>
-  <si>
     <t>Day</t>
   </si>
   <si>
@@ -209,6 +197,21 @@
   </si>
   <si>
     <t>Felix Monday</t>
+  </si>
+  <si>
+    <t>Denver Sweatz</t>
+  </si>
+  <si>
+    <t>Boundary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hopewell Ntuli </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liqhawe Pepeta </t>
+  </si>
+  <si>
+    <t>Dave Sanusi</t>
   </si>
 </sst>
 </file>
@@ -934,16 +937,16 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="K1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="L1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="M1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -958,10 +961,10 @@
       </c>
       <c r="D2" t="str" cm="1">
         <f t="array" ref="D2:F2">'Knockout Grid'!A5:C5</f>
-        <v>G1W</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
+        <v>Denver Sweatz</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Boundary</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -999,10 +1002,10 @@
       </c>
       <c r="G3" t="str" cm="1">
         <f t="array" ref="G3:I3">'Knockout Grid'!A10:C10</f>
-        <v>G2R</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
+        <v>Dave Sanusi</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Community House</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1163,7 +1166,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K8" s="12">
         <v>46172</v>
@@ -1404,10 +1407,10 @@
       </c>
       <c r="D16" t="str" cm="1">
         <f t="array" ref="D16:F16">'Knockout Grid'!A61:C61</f>
-        <v>G1R</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
+        <v xml:space="preserve">Hopewell Ntuli </v>
+      </c>
+      <c r="E16" t="str">
+        <v>CPUT</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1423,7 +1426,7 @@
         <v>0</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K16" s="12">
         <v>46172</v>
@@ -1457,10 +1460,10 @@
       </c>
       <c r="G17" t="str" cm="1">
         <f t="array" ref="G17:I17">'Knockout Grid'!A66:C66</f>
-        <v>G2W</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
+        <v xml:space="preserve">Liqhawe Pepeta </v>
+      </c>
+      <c r="H17" t="str">
+        <v>CPUT</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1476,28 +1479,28 @@
       <c r="C18">
         <v>16</v>
       </c>
-      <c r="D18" cm="1">
+      <c r="D18" t="str" cm="1">
         <f t="array" ref="D18:F18">'Knockout Grid'!F7:H7</f>
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
+        <v>Denver Sweatz</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Boundary</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
-      <c r="G18" cm="1">
+      <c r="G18" t="str" cm="1">
         <f t="array" ref="G18:I18">'Knockout Grid'!F8:H8</f>
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
+        <v>Dave Sanusi</v>
+      </c>
+      <c r="H18" t="str">
+        <v>Community House</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K18" s="12">
         <v>46172</v>
@@ -1540,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K19" s="12">
         <v>46172</v>
@@ -1583,7 +1586,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K20" s="12">
         <v>46172</v>
@@ -1626,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K21" s="12">
         <v>46172</v>
@@ -1658,18 +1661,18 @@
       <c r="F22">
         <v>0</v>
       </c>
-      <c r="G22" cm="1">
+      <c r="G22" t="str" cm="1">
         <f t="array" ref="G22:I22">'Knockout Grid'!F40:H40</f>
-        <v>0</v>
-      </c>
-      <c r="H22">
-        <v>0</v>
+        <v>Jihaan Jacobs</v>
+      </c>
+      <c r="H22" t="str">
+        <v>Ravens</v>
       </c>
       <c r="I22">
         <v>0</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K22" s="12">
         <v>46172</v>
@@ -1712,7 +1715,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K23" s="12">
         <v>46172</v>
@@ -1755,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K24" s="12">
         <v>46172</v>
@@ -1787,18 +1790,18 @@
       <c r="F25">
         <v>0</v>
       </c>
-      <c r="G25" cm="1">
+      <c r="G25" t="str" cm="1">
         <f t="array" ref="G25:I25">'Knockout Grid'!F64:H64</f>
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
+        <v xml:space="preserve">Liqhawe Pepeta </v>
+      </c>
+      <c r="H25" t="str">
+        <v>CPUT</v>
       </c>
       <c r="I25">
         <v>0</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K25" s="12">
         <v>46172</v>
@@ -1841,7 +1844,7 @@
         <v>0</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K26" s="12">
         <v>46172</v>
@@ -1884,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K27" s="12">
         <v>46172</v>
@@ -1927,7 +1930,7 @@
         <v>0</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K28" s="12">
         <v>46172</v>
@@ -1970,7 +1973,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K29" s="12">
         <v>46172</v>
@@ -2013,7 +2016,7 @@
         <v>0</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K30" s="12">
         <v>46172</v>
@@ -2056,7 +2059,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K31" s="12">
         <v>46172</v>
@@ -2099,7 +2102,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K32" s="12">
         <v>46172</v>
@@ -2153,7 +2156,7 @@
   <sheetData>
     <row r="1" spans="1:23" ht="34.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="17" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -2180,7 +2183,7 @@
     </row>
     <row r="2" spans="1:23" ht="34.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="17" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" s="17"/>
@@ -2207,35 +2210,35 @@
     </row>
     <row r="3" spans="1:23" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A3" s="18" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B3" s="18"/>
       <c r="C3" s="18"/>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="18" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G3" s="18"/>
       <c r="H3" s="18"/>
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
       <c r="K3" s="18" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L3" s="18"/>
       <c r="M3" s="18"/>
       <c r="N3" s="8"/>
       <c r="O3" s="8"/>
       <c r="P3" s="18" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Q3" s="18"/>
       <c r="R3" s="18"/>
       <c r="S3" s="8"/>
       <c r="T3" s="8"/>
       <c r="U3" s="18" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="V3" s="18"/>
       <c r="W3" s="18"/>
@@ -2253,13 +2256,15 @@
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="10"/>
+        <v>45</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>46</v>
+      </c>
       <c r="C5" s="11"/>
       <c r="D5" s="2"/>
       <c r="F5" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G5" s="12">
         <v>46172</v>
@@ -2273,7 +2278,7 @@
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="11"/>
@@ -2291,8 +2296,12 @@
     <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="D7" s="4"/>
       <c r="E7" s="5"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="10"/>
+      <c r="F7" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>46</v>
+      </c>
       <c r="H7" s="11"/>
       <c r="I7" s="2"/>
     </row>
@@ -2307,21 +2316,25 @@
         <v>2</v>
       </c>
       <c r="D8" s="4"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="10"/>
+      <c r="F8" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>32</v>
+      </c>
       <c r="H8" s="11"/>
       <c r="I8" s="1"/>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="11"/>
       <c r="D9" s="5"/>
       <c r="I9" s="4"/>
       <c r="K9" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L9" s="12">
         <v>46172</v>
@@ -2335,9 +2348,11 @@
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="10"/>
+        <v>49</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>32</v>
+      </c>
       <c r="C10" s="11"/>
       <c r="I10" s="4"/>
       <c r="K10">
@@ -2376,15 +2391,15 @@
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="2"/>
       <c r="F13" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G13" s="12">
         <v>46172</v>
@@ -2399,7 +2414,7 @@
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
@@ -2420,10 +2435,10 @@
       <c r="D15" s="4"/>
       <c r="E15" s="5"/>
       <c r="F15" s="9" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H15" s="11"/>
       <c r="I15" s="5"/>
@@ -2441,24 +2456,24 @@
       </c>
       <c r="D16" s="4"/>
       <c r="F16" s="9" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H16" s="11"/>
       <c r="N16" s="4"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B17" s="10"/>
       <c r="C17" s="11"/>
       <c r="D17" s="5"/>
       <c r="N17" s="4"/>
       <c r="P17" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Q17" s="12">
         <v>46172</v>
@@ -2472,10 +2487,10 @@
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C18" s="11"/>
       <c r="N18" s="4"/>
@@ -2515,15 +2530,15 @@
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C21" s="11"/>
       <c r="D21" s="2"/>
       <c r="F21" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G21" s="12">
         <v>46172</v>
@@ -2540,7 +2555,7 @@
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B22" s="10"/>
       <c r="C22" s="11"/>
@@ -2563,10 +2578,10 @@
       <c r="D23" s="4"/>
       <c r="E23" s="5"/>
       <c r="F23" s="9" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H23" s="11"/>
       <c r="I23" s="2"/>
@@ -2585,10 +2600,10 @@
       </c>
       <c r="D24" s="4"/>
       <c r="F24" s="9" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H24" s="11"/>
       <c r="I24" s="1"/>
@@ -2602,7 +2617,7 @@
       <c r="D25" s="5"/>
       <c r="I25" s="4"/>
       <c r="K25" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L25" s="12">
         <v>46172</v>
@@ -2618,10 +2633,10 @@
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C26" s="11"/>
       <c r="I26" s="4"/>
@@ -2639,7 +2654,7 @@
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B27" s="12">
         <v>46172</v>
@@ -2676,15 +2691,15 @@
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C29" s="11"/>
       <c r="D29" s="2"/>
       <c r="F29" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G29" s="12">
         <v>46172</v>
@@ -2700,10 +2715,10 @@
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C30" s="11"/>
       <c r="D30" s="3"/>
@@ -2740,17 +2755,17 @@
       </c>
       <c r="D32" s="4"/>
       <c r="F32" s="9" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H32" s="11"/>
       <c r="S32" s="4"/>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B33" s="10"/>
       <c r="C33" s="11"/>
@@ -2759,15 +2774,15 @@
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C34" s="11"/>
       <c r="S34" s="4"/>
       <c r="U34" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="V34" s="12">
         <v>46172</v>
@@ -2803,15 +2818,15 @@
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C37" s="11"/>
       <c r="D37" s="2"/>
       <c r="F37" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G37" s="12">
         <v>46172</v>
@@ -2827,7 +2842,7 @@
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B38" s="10"/>
       <c r="C38" s="11"/>
@@ -2847,10 +2862,10 @@
       <c r="D39" s="4"/>
       <c r="E39" s="5"/>
       <c r="F39" s="9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H39" s="11"/>
       <c r="I39" s="2"/>
@@ -2867,22 +2882,26 @@
         <v>10</v>
       </c>
       <c r="D40" s="4"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="10"/>
+      <c r="F40" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G40" s="10" t="s">
+        <v>29</v>
+      </c>
       <c r="H40" s="11"/>
       <c r="I40" s="1"/>
       <c r="S40" s="4"/>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41" s="9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B41" s="10"/>
       <c r="C41" s="11"/>
       <c r="D41" s="5"/>
       <c r="I41" s="4"/>
       <c r="K41" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L41" s="12">
         <v>46172</v>
@@ -2897,10 +2916,10 @@
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C42" s="11"/>
       <c r="I42" s="4"/>
@@ -2945,15 +2964,15 @@
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A45" s="9" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C45" s="11"/>
       <c r="D45" s="2"/>
       <c r="F45" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G45" s="12">
         <v>46172</v>
@@ -2990,10 +3009,10 @@
       <c r="D47" s="4"/>
       <c r="E47" s="5"/>
       <c r="F47" s="9" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H47" s="11"/>
       <c r="I47" s="5"/>
@@ -3012,10 +3031,10 @@
       </c>
       <c r="D48" s="4"/>
       <c r="F48" s="9" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="H48" s="11"/>
       <c r="N48" s="4"/>
@@ -3023,7 +3042,7 @@
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49" s="9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B49" s="10"/>
       <c r="C49" s="11"/>
@@ -3033,15 +3052,15 @@
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C50" s="11"/>
       <c r="N50" s="4"/>
       <c r="P50" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Q50" s="12">
         <v>46172</v>
@@ -3078,15 +3097,15 @@
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53" s="9" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C53" s="11"/>
       <c r="D53" s="2"/>
       <c r="F53" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G53" s="12">
         <v>46172</v>
@@ -3102,7 +3121,7 @@
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B54" s="10"/>
       <c r="C54" s="11"/>
@@ -3122,10 +3141,10 @@
       <c r="D55" s="4"/>
       <c r="E55" s="5"/>
       <c r="F55" s="9" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H55" s="11"/>
       <c r="I55" s="2"/>
@@ -3143,10 +3162,10 @@
       </c>
       <c r="D56" s="4"/>
       <c r="F56" s="9" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H56" s="11"/>
       <c r="I56" s="1"/>
@@ -3154,14 +3173,14 @@
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57" s="9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B57" s="10"/>
       <c r="C57" s="11"/>
       <c r="D57" s="5"/>
       <c r="I57" s="4"/>
       <c r="K57" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L57" s="12">
         <v>46172</v>
@@ -3176,10 +3195,10 @@
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58" s="9" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C58" s="11"/>
       <c r="I58" s="4"/>
@@ -3196,7 +3215,7 @@
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B59" s="12">
         <v>46172</v>
@@ -3231,13 +3250,15 @@
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B61" s="10"/>
+        <v>47</v>
+      </c>
+      <c r="B61" s="10" t="s">
+        <v>39</v>
+      </c>
       <c r="C61" s="11"/>
       <c r="D61" s="2"/>
       <c r="F61" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G61" s="12">
         <v>46172</v>
@@ -3251,10 +3272,10 @@
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A62" s="9" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C62" s="11"/>
       <c r="D62" s="3"/>
@@ -3288,8 +3309,12 @@
         <v>16</v>
       </c>
       <c r="D64" s="4"/>
-      <c r="F64" s="9"/>
-      <c r="G64" s="10"/>
+      <c r="F64" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="G64" s="10" t="s">
+        <v>39</v>
+      </c>
       <c r="H64" s="11"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -3302,9 +3327,11 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B66" s="10"/>
+        <v>48</v>
+      </c>
+      <c r="B66" s="10" t="s">
+        <v>39</v>
+      </c>
       <c r="C66" s="11"/>
     </row>
   </sheetData>

--- a/Knockouts/5thAndBelow.xlsx
+++ b/Knockouts/5thAndBelow.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Ravens Seniors\Knockouts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D2FC43B-71AC-483C-9B41-649DEBBE3F03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{059E37EE-1931-45F4-A769-8F1F285578EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" activeTab="1" xr2:uid="{6F46E828-8FFD-4531-838C-1A16471CA10A}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="51">
   <si>
     <t>Match</t>
   </si>
@@ -212,6 +212,9 @@
   </si>
   <si>
     <t>Dave Sanusi</t>
+  </si>
+  <si>
+    <t>WO</t>
   </si>
 </sst>
 </file>
@@ -1163,7 +1166,7 @@
         <v>Community House</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J8" s="6" t="s">
         <v>21</v>
@@ -1423,7 +1426,7 @@
         <v>Goodwood</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J16" s="6" t="s">
         <v>21</v>
@@ -1487,7 +1490,7 @@
         <v>Boundary</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G18" t="str" cm="1">
         <f t="array" ref="G18:I18">'Knockout Grid'!F8:H8</f>
@@ -1496,8 +1499,8 @@
       <c r="H18" t="str">
         <v>Community House</v>
       </c>
-      <c r="I18">
-        <v>0</v>
+      <c r="I18" t="str">
+        <v>WO</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>21</v>
@@ -1530,7 +1533,7 @@
         <v>Community House</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="str" cm="1">
         <f t="array" ref="G19:I19">'Knockout Grid'!F16:H16</f>
@@ -1540,7 +1543,7 @@
         <v>Community House</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J19" s="6" t="s">
         <v>21</v>
@@ -1573,7 +1576,7 @@
         <v>Ravens</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G20" t="str" cm="1">
         <f t="array" ref="G20:I20">'Knockout Grid'!F24:H24</f>
@@ -1582,8 +1585,8 @@
       <c r="H20" t="str">
         <v>Community House</v>
       </c>
-      <c r="I20">
-        <v>0</v>
+      <c r="I20" t="str">
+        <v>WO</v>
       </c>
       <c r="J20" s="6" t="s">
         <v>21</v>
@@ -1608,15 +1611,15 @@
       <c r="C21">
         <v>16</v>
       </c>
-      <c r="D21" cm="1">
+      <c r="D21" t="str" cm="1">
         <f t="array" ref="D21:F21">'Knockout Grid'!F31:H31</f>
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
+        <v>Felix Monday</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Community House</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G21" t="str" cm="1">
         <f t="array" ref="G21:I21">'Knockout Grid'!F32:H32</f>
@@ -1626,7 +1629,7 @@
         <v>Goodwood</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21" s="6" t="s">
         <v>21</v>
@@ -1659,7 +1662,7 @@
         <v>Ravens</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G22" t="str" cm="1">
         <f t="array" ref="G22:I22">'Knockout Grid'!F40:H40</f>
@@ -1669,7 +1672,7 @@
         <v>Ravens</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" s="6" t="s">
         <v>21</v>
@@ -1712,7 +1715,7 @@
         <v>CPUT</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>21</v>
@@ -1745,7 +1748,7 @@
         <v>Goodwood</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G24" t="str" cm="1">
         <f t="array" ref="G24:I24">'Knockout Grid'!F56:H56</f>
@@ -1755,7 +1758,7 @@
         <v>Ravens</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J24" s="6" t="s">
         <v>21</v>
@@ -1780,12 +1783,12 @@
       <c r="C25">
         <v>16</v>
       </c>
-      <c r="D25" cm="1">
+      <c r="D25" t="str" cm="1">
         <f t="array" ref="D25:F25">'Knockout Grid'!F63:H63</f>
-        <v>0</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
+        <v>Pedro Fortuin</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Goodwood</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1798,7 +1801,7 @@
         <v>CPUT</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J25" s="6" t="s">
         <v>21</v>
@@ -1823,22 +1826,22 @@
       <c r="C26" t="s">
         <v>9</v>
       </c>
-      <c r="D26" cm="1">
+      <c r="D26" t="str" cm="1">
         <f t="array" ref="D26:F26">'Knockout Grid'!K11:M11</f>
-        <v>0</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
+        <v>Denver Sweatz</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Boundary</v>
       </c>
       <c r="F26">
         <v>0</v>
       </c>
-      <c r="G26" cm="1">
+      <c r="G26" t="str" cm="1">
         <f t="array" ref="G26:I26">'Knockout Grid'!K12:M12</f>
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>0</v>
+        <v>Lawrence Omadeli</v>
+      </c>
+      <c r="H26" t="str">
+        <v>Community House</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -1866,22 +1869,22 @@
       <c r="C27" t="s">
         <v>9</v>
       </c>
-      <c r="D27" cm="1">
+      <c r="D27" t="str" cm="1">
         <f t="array" ref="D27:F27">'Knockout Grid'!K27:M27</f>
-        <v>0</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
+        <v>Gideon Stompies</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Ravens</v>
       </c>
       <c r="F27">
         <v>0</v>
       </c>
-      <c r="G27" cm="1">
+      <c r="G27" t="str" cm="1">
         <f t="array" ref="G27:I27">'Knockout Grid'!K28:M28</f>
-        <v>0</v>
-      </c>
-      <c r="H27">
-        <v>0</v>
+        <v>Felix Monday</v>
+      </c>
+      <c r="H27" t="str">
+        <v>Community House</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -1909,22 +1912,22 @@
       <c r="C28" t="s">
         <v>9</v>
       </c>
-      <c r="D28" cm="1">
+      <c r="D28" t="str" cm="1">
         <f t="array" ref="D28:F28">'Knockout Grid'!K43:M43</f>
-        <v>0</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
+        <v>Angeline Wood</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Ravens</v>
       </c>
       <c r="F28">
         <v>0</v>
       </c>
-      <c r="G28" cm="1">
+      <c r="G28" t="str" cm="1">
         <f t="array" ref="G28:I28">'Knockout Grid'!K44:M44</f>
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
+        <v xml:space="preserve">Scelo Mkhetho </v>
+      </c>
+      <c r="H28" t="str">
+        <v>CPUT</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -1952,22 +1955,22 @@
       <c r="C29" t="s">
         <v>9</v>
       </c>
-      <c r="D29" cm="1">
+      <c r="D29" t="str" cm="1">
         <f t="array" ref="D29:F29">'Knockout Grid'!K59:M59</f>
-        <v>0</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
+        <v>Jyante Jacobs</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Ravens</v>
       </c>
       <c r="F29">
         <v>0</v>
       </c>
-      <c r="G29" cm="1">
+      <c r="G29" t="str" cm="1">
         <f t="array" ref="G29:I29">'Knockout Grid'!K60:M60</f>
-        <v>0</v>
-      </c>
-      <c r="H29">
-        <v>0</v>
+        <v xml:space="preserve">Liqhawe Pepeta </v>
+      </c>
+      <c r="H29" t="str">
+        <v>CPUT</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -2147,6 +2150,7 @@
     <col min="5" max="5" width="1.7109375" customWidth="1"/>
     <col min="9" max="9" width="4" customWidth="1"/>
     <col min="10" max="10" width="1.85546875" customWidth="1"/>
+    <col min="11" max="11" width="16.140625" customWidth="1"/>
     <col min="12" max="12" width="9.140625" style="7"/>
     <col min="14" max="14" width="4.140625" customWidth="1"/>
     <col min="15" max="15" width="3.42578125" customWidth="1"/>
@@ -2302,7 +2306,9 @@
       <c r="G7" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="H7" s="11"/>
+      <c r="H7" s="11">
+        <v>3</v>
+      </c>
       <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
@@ -2322,7 +2328,9 @@
       <c r="G8" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="11"/>
+      <c r="H8" s="11" t="s">
+        <v>50</v>
+      </c>
       <c r="I8" s="1"/>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.25">
@@ -2368,8 +2376,12 @@
     <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="I11" s="4"/>
       <c r="J11" s="2"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="15"/>
+      <c r="K11" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="L11" s="15" t="s">
+        <v>46</v>
+      </c>
       <c r="M11" s="11"/>
       <c r="N11" s="2"/>
     </row>
@@ -2384,8 +2396,12 @@
         <v>3</v>
       </c>
       <c r="I12" s="4"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="15"/>
+      <c r="K12" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="L12" s="15" t="s">
+        <v>32</v>
+      </c>
       <c r="M12" s="11"/>
       <c r="N12" s="1"/>
     </row>
@@ -2440,7 +2456,9 @@
       <c r="G15" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="H15" s="11"/>
+      <c r="H15" s="11">
+        <v>1</v>
+      </c>
       <c r="I15" s="5"/>
       <c r="N15" s="4"/>
     </row>
@@ -2461,7 +2479,9 @@
       <c r="G16" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="H16" s="11"/>
+      <c r="H16" s="11">
+        <v>3</v>
+      </c>
       <c r="N16" s="4"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
@@ -2583,7 +2603,9 @@
       <c r="G23" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="H23" s="11"/>
+      <c r="H23" s="11">
+        <v>3</v>
+      </c>
       <c r="I23" s="2"/>
       <c r="N23" s="4"/>
       <c r="S23" s="4"/>
@@ -2605,7 +2627,9 @@
       <c r="G24" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="H24" s="11"/>
+      <c r="H24" s="11" t="s">
+        <v>50</v>
+      </c>
       <c r="I24" s="1"/>
       <c r="N24" s="4"/>
       <c r="S24" s="4"/>
@@ -2667,8 +2691,12 @@
       </c>
       <c r="I27" s="4"/>
       <c r="J27" s="2"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="15"/>
+      <c r="K27" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="L27" s="15" t="s">
+        <v>29</v>
+      </c>
       <c r="M27" s="11"/>
       <c r="N27" s="5"/>
       <c r="S27" s="4"/>
@@ -2684,8 +2712,12 @@
         <v>7</v>
       </c>
       <c r="I28" s="4"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="15"/>
+      <c r="K28" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="L28" s="15" t="s">
+        <v>32</v>
+      </c>
       <c r="M28" s="11"/>
       <c r="S28" s="4"/>
     </row>
@@ -2696,7 +2728,9 @@
       <c r="B29" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C29" s="11"/>
+      <c r="C29" s="11">
+        <v>0</v>
+      </c>
       <c r="D29" s="2"/>
       <c r="F29" s="6" t="s">
         <v>21</v>
@@ -2720,7 +2754,9 @@
       <c r="B30" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C30" s="11"/>
+      <c r="C30" s="11">
+        <v>3</v>
+      </c>
       <c r="D30" s="3"/>
       <c r="F30">
         <v>20</v>
@@ -2737,9 +2773,15 @@
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="D31" s="4"/>
       <c r="E31" s="5"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="11"/>
+      <c r="F31" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="H31" s="11">
+        <v>3</v>
+      </c>
       <c r="I31" s="5"/>
       <c r="S31" s="4"/>
     </row>
@@ -2760,7 +2802,9 @@
       <c r="G32" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="H32" s="11"/>
+      <c r="H32" s="11">
+        <v>2</v>
+      </c>
       <c r="S32" s="4"/>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.25">
@@ -2867,7 +2911,9 @@
       <c r="G39" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="H39" s="11"/>
+      <c r="H39" s="11">
+        <v>3</v>
+      </c>
       <c r="I39" s="2"/>
       <c r="S39" s="4"/>
     </row>
@@ -2888,7 +2934,9 @@
       <c r="G40" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="H40" s="11"/>
+      <c r="H40" s="11">
+        <v>2</v>
+      </c>
       <c r="I40" s="1"/>
       <c r="S40" s="4"/>
     </row>
@@ -2939,8 +2987,12 @@
       <c r="C43" s="13"/>
       <c r="I43" s="4"/>
       <c r="J43" s="2"/>
-      <c r="K43" s="9"/>
-      <c r="L43" s="15"/>
+      <c r="K43" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="L43" s="15" t="s">
+        <v>29</v>
+      </c>
       <c r="M43" s="11"/>
       <c r="N43" s="2"/>
       <c r="S43" s="4"/>
@@ -2956,8 +3008,12 @@
         <v>11</v>
       </c>
       <c r="I44" s="4"/>
-      <c r="K44" s="9"/>
-      <c r="L44" s="15"/>
+      <c r="K44" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="L44" s="15" t="s">
+        <v>39</v>
+      </c>
       <c r="M44" s="11"/>
       <c r="N44" s="1"/>
       <c r="S44" s="4"/>
@@ -3014,7 +3070,9 @@
       <c r="G47" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="H47" s="11"/>
+      <c r="H47" s="11">
+        <v>0</v>
+      </c>
       <c r="I47" s="5"/>
       <c r="N47" s="4"/>
       <c r="S47" s="4"/>
@@ -3036,7 +3094,9 @@
       <c r="G48" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="H48" s="11"/>
+      <c r="H48" s="11">
+        <v>3</v>
+      </c>
       <c r="N48" s="4"/>
       <c r="S48" s="4"/>
     </row>
@@ -3146,7 +3206,9 @@
       <c r="G55" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="H55" s="11"/>
+      <c r="H55" s="11">
+        <v>2</v>
+      </c>
       <c r="I55" s="2"/>
       <c r="N55" s="4"/>
     </row>
@@ -3167,7 +3229,9 @@
       <c r="G56" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="H56" s="11"/>
+      <c r="H56" s="11">
+        <v>3</v>
+      </c>
       <c r="I56" s="1"/>
       <c r="N56" s="4"/>
     </row>
@@ -3228,8 +3292,12 @@
       </c>
       <c r="I59" s="4"/>
       <c r="J59" s="2"/>
-      <c r="K59" s="9"/>
-      <c r="L59" s="15"/>
+      <c r="K59" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L59" s="15" t="s">
+        <v>29</v>
+      </c>
       <c r="M59" s="11"/>
       <c r="N59" s="5"/>
     </row>
@@ -3244,8 +3312,12 @@
         <v>15</v>
       </c>
       <c r="I60" s="4"/>
-      <c r="K60" s="9"/>
-      <c r="L60" s="15"/>
+      <c r="K60" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="L60" s="15" t="s">
+        <v>39</v>
+      </c>
       <c r="M60" s="11"/>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.25">
@@ -3255,7 +3327,9 @@
       <c r="B61" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C61" s="11"/>
+      <c r="C61" s="11">
+        <v>0</v>
+      </c>
       <c r="D61" s="2"/>
       <c r="F61" s="6" t="s">
         <v>21</v>
@@ -3277,7 +3351,9 @@
       <c r="B62" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C62" s="11"/>
+      <c r="C62" s="11">
+        <v>3</v>
+      </c>
       <c r="D62" s="3"/>
       <c r="F62">
         <v>24</v>
@@ -3293,9 +3369,15 @@
     <row r="63" spans="1:19" x14ac:dyDescent="0.25">
       <c r="D63" s="4"/>
       <c r="E63" s="5"/>
-      <c r="F63" s="9"/>
-      <c r="G63" s="10"/>
-      <c r="H63" s="11"/>
+      <c r="F63" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G63" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="H63" s="11">
+        <v>0</v>
+      </c>
       <c r="I63" s="5"/>
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.25">
@@ -3315,7 +3397,9 @@
       <c r="G64" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="H64" s="11"/>
+      <c r="H64" s="11">
+        <v>3</v>
+      </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="9" t="s">

--- a/Knockouts/5thAndBelow.xlsx
+++ b/Knockouts/5thAndBelow.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Ravens Seniors\Knockouts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{059E37EE-1931-45F4-A769-8F1F285578EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25FDAEBF-C885-46B3-B271-8B1876B87A3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" activeTab="1" xr2:uid="{6F46E828-8FFD-4531-838C-1A16471CA10A}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="51">
   <si>
     <t>Match</t>
   </si>
@@ -1834,7 +1834,7 @@
         <v>Boundary</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G26" t="str" cm="1">
         <f t="array" ref="G26:I26">'Knockout Grid'!K12:M12</f>
@@ -1877,7 +1877,7 @@
         <v>Ravens</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G27" t="str" cm="1">
         <f t="array" ref="G27:I27">'Knockout Grid'!K28:M28</f>
@@ -1930,7 +1930,7 @@
         <v>CPUT</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J28" s="6" t="s">
         <v>21</v>
@@ -1973,7 +1973,7 @@
         <v>CPUT</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J29" s="6" t="s">
         <v>21</v>
@@ -1998,25 +1998,25 @@
       <c r="C30" t="s">
         <v>10</v>
       </c>
-      <c r="D30" cm="1">
+      <c r="D30" t="str" cm="1">
         <f t="array" ref="D30:F30">'Knockout Grid'!P19:R19</f>
-        <v>0</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
+        <v>Denver Sweatz</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Boundary</v>
       </c>
       <c r="F30">
-        <v>0</v>
-      </c>
-      <c r="G30" cm="1">
+        <v>1</v>
+      </c>
+      <c r="G30" t="str" cm="1">
         <f t="array" ref="G30:I30">'Knockout Grid'!P20:R20</f>
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <v>0</v>
+        <v>Gideon Stompies</v>
+      </c>
+      <c r="H30" t="str">
+        <v>Ravens</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J30" s="6" t="s">
         <v>21</v>
@@ -2041,25 +2041,25 @@
       <c r="C31" t="s">
         <v>10</v>
       </c>
-      <c r="D31" cm="1">
+      <c r="D31" t="str" cm="1">
         <f t="array" ref="D31:F31">'Knockout Grid'!P51:R51</f>
-        <v>0</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
+        <v xml:space="preserve">Scelo Mkhetho </v>
+      </c>
+      <c r="E31" t="str">
+        <v>CPUT</v>
       </c>
       <c r="F31">
         <v>0</v>
       </c>
-      <c r="G31" cm="1">
+      <c r="G31" t="str" cm="1">
         <f t="array" ref="G31:I31">'Knockout Grid'!P52:R52</f>
-        <v>0</v>
-      </c>
-      <c r="H31">
-        <v>0</v>
+        <v xml:space="preserve">Liqhawe Pepeta </v>
+      </c>
+      <c r="H31" t="str">
+        <v>CPUT</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J31" s="6" t="s">
         <v>21</v>
@@ -2084,22 +2084,22 @@
       <c r="C32" t="s">
         <v>11</v>
       </c>
-      <c r="D32" cm="1">
+      <c r="D32" t="str" cm="1">
         <f t="array" ref="D32:F32">'Knockout Grid'!U35:W35</f>
-        <v>0</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
+        <v>Gideon Stompies</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Ravens</v>
       </c>
       <c r="F32">
         <v>0</v>
       </c>
-      <c r="G32" cm="1">
+      <c r="G32" t="str" cm="1">
         <f t="array" ref="G32:I32">'Knockout Grid'!U36:W36</f>
-        <v>0</v>
-      </c>
-      <c r="H32">
-        <v>0</v>
+        <v xml:space="preserve">Liqhawe Pepeta </v>
+      </c>
+      <c r="H32" t="str">
+        <v>CPUT</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -2382,7 +2382,9 @@
       <c r="L11" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="M11" s="11"/>
+      <c r="M11" s="11">
+        <v>3</v>
+      </c>
       <c r="N11" s="2"/>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.25">
@@ -2402,7 +2404,9 @@
       <c r="L12" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="M12" s="11"/>
+      <c r="M12" s="11">
+        <v>0</v>
+      </c>
       <c r="N12" s="1"/>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.25">
@@ -2527,9 +2531,15 @@
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="N19" s="4"/>
       <c r="O19" s="2"/>
-      <c r="P19" s="9"/>
-      <c r="Q19" s="15"/>
-      <c r="R19" s="11"/>
+      <c r="P19" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q19" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="R19" s="11">
+        <v>1</v>
+      </c>
       <c r="S19" s="2"/>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
@@ -2543,9 +2553,15 @@
         <v>5</v>
       </c>
       <c r="N20" s="4"/>
-      <c r="P20" s="9"/>
-      <c r="Q20" s="15"/>
-      <c r="R20" s="11"/>
+      <c r="P20" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q20" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="R20" s="11">
+        <v>3</v>
+      </c>
       <c r="S20" s="1"/>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
@@ -2697,7 +2713,9 @@
       <c r="L27" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="M27" s="11"/>
+      <c r="M27" s="11">
+        <v>3</v>
+      </c>
       <c r="N27" s="5"/>
       <c r="S27" s="4"/>
     </row>
@@ -2718,7 +2736,9 @@
       <c r="L28" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="M28" s="11"/>
+      <c r="M28" s="11">
+        <v>0</v>
+      </c>
       <c r="S28" s="4"/>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
@@ -2841,8 +2861,12 @@
     <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="S35" s="4"/>
       <c r="T35" s="2"/>
-      <c r="U35" s="9"/>
-      <c r="V35" s="15"/>
+      <c r="U35" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="V35" s="15" t="s">
+        <v>29</v>
+      </c>
       <c r="W35" s="11"/>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.25">
@@ -2856,8 +2880,12 @@
         <v>9</v>
       </c>
       <c r="S36" s="4"/>
-      <c r="U36" s="9"/>
-      <c r="V36" s="15"/>
+      <c r="U36" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="V36" s="15" t="s">
+        <v>39</v>
+      </c>
       <c r="W36" s="11"/>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.25">
@@ -2993,7 +3021,9 @@
       <c r="L43" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="M43" s="11"/>
+      <c r="M43" s="11">
+        <v>0</v>
+      </c>
       <c r="N43" s="2"/>
       <c r="S43" s="4"/>
     </row>
@@ -3014,7 +3044,9 @@
       <c r="L44" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="M44" s="11"/>
+      <c r="M44" s="11">
+        <v>3</v>
+      </c>
       <c r="N44" s="1"/>
       <c r="S44" s="4"/>
     </row>
@@ -3135,9 +3167,15 @@
     <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="N51" s="4"/>
       <c r="O51" s="2"/>
-      <c r="P51" s="9"/>
-      <c r="Q51" s="15"/>
-      <c r="R51" s="11"/>
+      <c r="P51" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q51" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="R51" s="11">
+        <v>0</v>
+      </c>
       <c r="S51" s="5"/>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.25">
@@ -3151,9 +3189,15 @@
         <v>13</v>
       </c>
       <c r="N52" s="4"/>
-      <c r="P52" s="9"/>
-      <c r="Q52" s="15"/>
-      <c r="R52" s="11"/>
+      <c r="P52" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q52" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="R52" s="11">
+        <v>3</v>
+      </c>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53" s="9" t="s">
@@ -3298,7 +3342,9 @@
       <c r="L59" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="M59" s="11"/>
+      <c r="M59" s="11">
+        <v>0</v>
+      </c>
       <c r="N59" s="5"/>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.25">
@@ -3318,7 +3364,9 @@
       <c r="L60" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="M60" s="11"/>
+      <c r="M60" s="11">
+        <v>3</v>
+      </c>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61" s="9" t="s">

--- a/Knockouts/5thAndBelow.xlsx
+++ b/Knockouts/5thAndBelow.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Ravens Seniors\Knockouts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25FDAEBF-C885-46B3-B271-8B1876B87A3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0828649-8EDE-4777-9673-0B9ECBD98A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" activeTab="1" xr2:uid="{6F46E828-8FFD-4531-838C-1A16471CA10A}"/>
   </bookViews>
@@ -2092,7 +2092,7 @@
         <v>Ravens</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G32" t="str" cm="1">
         <f t="array" ref="G32:I32">'Knockout Grid'!U36:W36</f>
@@ -2102,7 +2102,7 @@
         <v>CPUT</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J32" s="6" t="s">
         <v>21</v>
@@ -2867,7 +2867,9 @@
       <c r="V35" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="W35" s="11"/>
+      <c r="W35" s="11">
+        <v>2</v>
+      </c>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
@@ -2886,7 +2888,9 @@
       <c r="V36" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="W36" s="11"/>
+      <c r="W36" s="11">
+        <v>3</v>
+      </c>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
